--- a/results/Int All Data -0.2/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.2/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.00162922525136582</v>
+        <v>-0.001453304206239666</v>
       </c>
       <c r="C3" t="n">
-        <v>-6.08403018791337e-05</v>
+        <v>-0.0001915570140811296</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0003854436127655936</v>
+        <v>0.0001475498734814884</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0005796029885661235</v>
+        <v>-0.0003460083479208709</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001536069631450021</v>
+        <v>-1.64028906213276e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.601183919763173e-05</v>
+        <v>-0.0001147773754049985</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0004210474662211783</v>
+        <v>-0.001701864403198804</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002421572085438227</v>
+        <v>-0.002220766628082232</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0009773270167796576</v>
+        <v>-5.49982552060246e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>4.94293250522282e-05</v>
+        <v>0.0001455379453722305</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001845565221509959</v>
+        <v>0.0005879941248358288</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0003552812789647452</v>
+        <v>-0.001765075323742089</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.003402446944754961</v>
+        <v>0.0007515158872647253</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.002348092412236284</v>
+        <v>-0.002964857902316747</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.00101747522251402</v>
+        <v>0.0002409148117301785</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007590508534510599</v>
+        <v>0.001590840288766423</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001433307514791445</v>
+        <v>-3.338510005780344e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001949169201353883</v>
+        <v>-0.002995178897906261</v>
       </c>
       <c r="T3" t="n">
-        <v>-7.186100620457102e-05</v>
+        <v>-0.0004659469901284897</v>
       </c>
       <c r="U3" t="n">
-        <v>5.116442476575714e-05</v>
+        <v>-0.0006873481110407376</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0006995452515067734</v>
+        <v>-0.001316015886959449</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0005372116106357051</v>
+        <v>-0.0002678740905994836</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002045998410372906</v>
+        <v>-0.0002340917336906222</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0001236581769794776</v>
+        <v>-0.000664064719047156</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002048719604303036</v>
+        <v>0.0008676708865184791</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001932458241779766</v>
+        <v>0.001966341138763903</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0005520754736077782</v>
+        <v>0.0002819503073877783</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0009050454154856359</v>
+        <v>-0.0002183431397505164</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003109939351232177</v>
+        <v>-0.001376400478164402</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.002681244637079202</v>
+        <v>4.84603469094767e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0003841357801777047</v>
+        <v>0.0006543234473733028</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0003704622612413322</v>
+        <v>-3.119674853550026e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0001916973446040815</v>
+        <v>0.0003470985507025559</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.0008104053121333476</v>
+        <v>0.0003615952106378795</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0005814427882555173</v>
+        <v>-0.002562584010128366</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.005808441580419287</v>
+        <v>0.009171355860414792</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.730396353929018e-05</v>
+        <v>0.0001353036497419946</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.001662956267749373</v>
+        <v>-0.0002192899242665036</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0002130712418702774</v>
+        <v>-0.0008947854070288855</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0007786113045015009</v>
+        <v>-0.001342183871733852</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0008095157971329304</v>
+        <v>-0.0003250692527879128</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.000462549063150135</v>
+        <v>0.001444833124511151</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.002846847033640204</v>
+        <v>0.003527529364123717</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0005044565841774273</v>
+        <v>0.0003450757247402702</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001158299252235999</v>
+        <v>-8.82932181302953e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.0006145174350214565</v>
+        <v>-0.0003589641645721797</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.001236022051889954</v>
+        <v>0.0001123929220376496</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0009868258380887572</v>
+        <v>-0.001061486454080073</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0003615128316692928</v>
+        <v>7.062888747502713e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0004798885438079059</v>
+        <v>0.0002216434142949319</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001489770824784422</v>
+        <v>-0.0004755021757010381</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0007586209110760345</v>
+        <v>-0.00192901096085603</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.003184765320383341</v>
+        <v>0.001757379977975735</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002457470864743861</v>
+        <v>-0.0001431802617938938</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1.873870086477992e-05</v>
+        <v>0.0002909907887240514</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0003256434984850743</v>
+        <v>-0.0002350384899605718</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0007852187307007376</v>
+        <v>7.711433914257778e-05</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.00298443794916127</v>
+        <v>-0.0005521845578602502</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0005449576720361027</v>
+        <v>-0.0001877655607108785</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.001308354334196145</v>
+        <v>0.001530136164498397</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0003303477418073808</v>
+        <v>0.0001969289066450142</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.001232631855759667</v>
+        <v>-0.001323542320685303</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0004376944822543726</v>
+        <v>-4.86500303966253e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0004989280211559132</v>
+        <v>-0.0001529856657815087</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.00104538316427977</v>
+        <v>0.0005224885539538959</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.0002654904328453389</v>
+        <v>-0.0008751268328730542</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001224825982223834</v>
+        <v>0.001147745524443372</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.00254999282595757</v>
+        <v>0.001781966360711871</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.001048470246782381</v>
+        <v>0.0006866557202998512</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.484220063500592e-06</v>
+        <v>8.678732424684977e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0008228186060788278</v>
+        <v>0.0008537453684581465</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0004600431239361481</v>
+        <v>0.0006327789303508825</v>
       </c>
       <c r="BW3" t="n">
-        <v>-7.169889295876363e-05</v>
+        <v>-3.820786176350231e-10</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.001501130521091171</v>
+        <v>-0.0005587760040734569</v>
       </c>
       <c r="BY3" t="n">
-        <v>-8.891675379003048e-05</v>
+        <v>2.63592438924632e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0001371607276745268</v>
+        <v>-0.0001550948435199029</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.60422395466098e-05</v>
+        <v>3.842988270053804e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0003037780813250401</v>
+        <v>0.001884952475508556</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0003196475289807621</v>
+        <v>0.0007000790094733722</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.001642039824970804</v>
+        <v>-0.0003522425782693761</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0007308954338240814</v>
+        <v>-0.0007691765206091039</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.000598758057112665</v>
+        <v>-0.0005319890476262768</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0006580154739032875</v>
+        <v>-0.0004047205634096928</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.000506212533780126</v>
+        <v>0.0002462422536032494</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.001054247974234937</v>
+        <v>0.0002290331193809447</v>
       </c>
       <c r="CJ3" t="n">
-        <v>8.639732221022991e-06</v>
+        <v>-2.781616319040725e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0003423603530465458</v>
+        <v>5.733995387905434e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.004512369706242743</v>
+        <v>0.0003070296176172571</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0003299294324023306</v>
+        <v>-0.0003746114987207582</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.0002294720606943778</v>
+        <v>-0.0001843044441352515</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.0001064075919970842</v>
+        <v>0.0003228806334010215</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.000139976861095521</v>
+        <v>0.0001762262496441435</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.0009709167431828635</v>
+        <v>0.0001840334872872163</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.002607598273662563</v>
+        <v>-0.00029493541911497</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.003635891421369609</v>
+        <v>-0.000576804692490962</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.00483041494790131</v>
+        <v>-0.0004942511982855457</v>
       </c>
       <c r="CU3" t="n">
-        <v>-6.305319028071188e-05</v>
+        <v>0.0001113519258661755</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0002143978672385183</v>
+        <v>-3.188273073830626e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.003084288262236357</v>
+        <v>-0.0006449166304240539</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.001157822996428226</v>
+        <v>0.0003172266027421622</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.000106409705616467</v>
+        <v>4.03562403623059e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0001999963674146632</v>
+        <v>-3.510150122142508e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0003975055470090605</v>
+        <v>0.0008024237240003498</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001779972035868014</v>
+        <v>-5.171949551419863e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>-5.16522007355824e-05</v>
+        <v>0.0001496058742411288</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0006802770414018888</v>
+        <v>0.0004970904736212445</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.004827456212276627</v>
+        <v>-0.0001341267684232749</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0006764187477333905</v>
+        <v>-0.000207418193756842</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.002774651386462933</v>
+        <v>-0.0006845806167026115</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.00119106873962601</v>
+        <v>-0.0002395370999172819</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0009201104871280985</v>
+        <v>-0.0001134406537489386</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.000692739599051384</v>
+        <v>0.0006333602748109846</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0001371069467757946</v>
+        <v>5.727374074269154e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.0001053354619861124</v>
+        <v>-0.0004705120123664374</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001531292928428087</v>
+        <v>-0.001791494130913829</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.002081419116450967</v>
+        <v>-0.001319703654681945</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.00294471225643966</v>
+        <v>-0.001024898193559088</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.0003513144784211353</v>
+        <v>-7.279813379273969e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.000146725342885452</v>
+        <v>9.655433806046501e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>6.286443512914075e-05</v>
+        <v>-1.096288596835304e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.001961142342938147</v>
+        <v>-0.001370138739059179</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001990531019289797</v>
+        <v>-0.0005369344817967968</v>
       </c>
       <c r="DV3" t="n">
-        <v>-1.069956340433942e-05</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0002078631887317628</v>
+        <v>-8.657949567366651e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0002359911011208104</v>
+        <v>0.0004495737342849682</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.003292366748491137</v>
+        <v>-0.001058667075568123</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0001650951796435307</v>
+        <v>-0.0001535974506015003</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0006437543661079947</v>
+        <v>-0.0005986221138214209</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.002861352475496429</v>
+        <v>-0.001557512674180952</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.000156080676555742</v>
+        <v>-0.0004860644819758064</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.000691831073945316</v>
+        <v>-0.0003279727320771664</v>
       </c>
       <c r="EE3" t="n">
-        <v>6.544475750882683e-05</v>
+        <v>9.916694776147983e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0002777101549247385</v>
+        <v>-0.0007352011487614574</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.000594927763140295</v>
+        <v>-0.000531573502123357</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0004360851134153798</v>
+        <v>1.353797025207436e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0002120710636478595</v>
+        <v>-0.000933878199479129</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0002480975488782489</v>
+        <v>-0.0003200459195265582</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.000623339703908241</v>
+        <v>0.0003367164401598743</v>
       </c>
       <c r="EL3" t="n">
-        <v>-9.597899293511958e-06</v>
+        <v>-3.548196848398355e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>5.557416540324931e-06</v>
+        <v>-0.000114900541645846</v>
       </c>
       <c r="EN3" t="n">
-        <v>5.901192570055947e-05</v>
+        <v>0.0001551629414624633</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>6.268428665355836e-06</v>
+        <v>8.199013772893772e-06</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0002623689264643392</v>
+        <v>-0.0005114266905331665</v>
       </c>
       <c r="ER3" t="n">
-        <v>7.387850051437494e-05</v>
+        <v>2.557099937632423e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-1.895981165966676e-05</v>
+        <v>0.0001679281647892872</v>
       </c>
       <c r="ET3" t="n">
-        <v>-7.887581176537644e-05</v>
+        <v>-3.534930776906253e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0006201998850196644</v>
+        <v>0.0001691623368899797</v>
       </c>
       <c r="EV3" t="n">
-        <v>-4.391774570039918e-05</v>
+        <v>9.757317521317698e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0004668959033587072</v>
+        <v>-0.0003412797478250873</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0002187816222192973</v>
+        <v>-0.000542739028814977</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0003144662917928242</v>
+        <v>0.0003647409690998071</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002471810708275046</v>
+        <v>0.00521375570065855</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001179396313984093</v>
+        <v>0.001218598325716814</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00176083536820097</v>
+        <v>0.001820386041277556</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001484083359323523</v>
+        <v>0.00270865307722738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005906604381450564</v>
+        <v>0.000675005707950698</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002209032664762244</v>
+        <v>0.002127509957463628</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002190808252999756</v>
+        <v>0.003612291967961548</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004685211541355455</v>
+        <v>0.005103686789786211</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001875862978288289</v>
+        <v>0.002274804579826197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005125673609591498</v>
+        <v>0.000568812396667663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004747573038236442</v>
+        <v>0.001073448430430973</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002633234390214082</v>
+        <v>0.001612330165811427</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007337882604277756</v>
+        <v>0.005972540705392266</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003582179244115301</v>
+        <v>0.006686537331511519</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001644058251520317</v>
+        <v>0.001281422178484917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007073679245190687</v>
+        <v>0.004413876608317052</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00139277860841655</v>
+        <v>0.002260484271785264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004349632992012312</v>
+        <v>0.008712061376442551</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006111040951568258</v>
+        <v>0.0009394942327985647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002374191123031239</v>
+        <v>0.001368593476184304</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001708441497584843</v>
+        <v>0.007440872638302191</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002695924812633838</v>
+        <v>0.001470473128738347</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005114923801601599</v>
+        <v>0.002253211158479704</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007806086309186646</v>
+        <v>0.001231364181516715</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00362264183797595</v>
+        <v>0.001940809056550352</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00806054829931851</v>
+        <v>0.005833168510017167</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001247236311931083</v>
+        <v>0.0003698525715557114</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003097634595147854</v>
+        <v>0.003172965076333476</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.003810221288801507</v>
+        <v>0.01030363452411013</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004684040072607921</v>
+        <v>0.009154183232850726</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004026794264253988</v>
+        <v>0.002644294861716032</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001066856205348244</v>
+        <v>0.001216409791865771</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007480721356051833</v>
+        <v>0.001102197391729603</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001797293369217943</v>
+        <v>0.001070602016985057</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005563922745142479</v>
+        <v>0.009175251312710469</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01156085161540554</v>
+        <v>0.01533436718697775</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00165977626902618</v>
+        <v>0.001206921538372415</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.003999530140719792</v>
+        <v>0.002956409180649969</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0017804694845762</v>
+        <v>0.00333751106910859</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002917013954980088</v>
+        <v>0.004986376783266845</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0011917837014156</v>
+        <v>0.0009593316774301471</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001907278225665308</v>
+        <v>0.002043933844211856</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005666784692887189</v>
+        <v>0.003986821415952746</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001771265514561491</v>
+        <v>0.0009072355679402165</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003269487412385034</v>
+        <v>0.004366769055513772</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001367293323742898</v>
+        <v>0.001565107490389888</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001671806933872152</v>
+        <v>0.002012443063812433</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002671922777208153</v>
+        <v>0.001238200979773042</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0003083671665885951</v>
+        <v>0.0009248016475888243</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001738531820227647</v>
+        <v>0.001366994537580947</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002045910440341377</v>
+        <v>0.001415883159275849</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.005179695207673161</v>
+        <v>0.007955437474310418</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004169790611180387</v>
+        <v>0.006575999790553345</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004098250839223956</v>
+        <v>0.0004309338649216763</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0005914240794730636</v>
+        <v>0.001245875288481248</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002987774528789765</v>
+        <v>0.001778111267955045</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.005378737518676703</v>
+        <v>0.003933974801154702</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005749822304206104</v>
+        <v>0.002942666751348673</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001393677756140061</v>
+        <v>0.001049162993957678</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.007013342057118991</v>
+        <v>0.004761047920126788</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002283404584101244</v>
+        <v>0.00173567989776414</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003918717632687953</v>
+        <v>0.004108142384740654</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001840537075705109</v>
+        <v>0.0007158545409544798</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001766612945514769</v>
+        <v>0.0007278918151501974</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003769191360955084</v>
+        <v>0.005485920044229176</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001125054837567503</v>
+        <v>0.002257541970873504</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002733068560834627</v>
+        <v>0.002901539715615204</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.005115566226287697</v>
+        <v>0.003672449591796796</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001888797100057161</v>
+        <v>0.002732606471893834</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002413482608567306</v>
+        <v>0.001157941411314659</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003579949847714794</v>
+        <v>0.002359013875808028</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002097155603406809</v>
+        <v>0.00111663657576381</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001329996158981768</v>
+        <v>2.623933494187934e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002836241545676131</v>
+        <v>0.001165725210400888</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003690983274639121</v>
+        <v>0.002057505419244882</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002869699213560643</v>
+        <v>0.003459547911822221</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001144237726150645</v>
+        <v>0.001744781965669642</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001469691981703934</v>
+        <v>0.002878533172017073</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002249356951332207</v>
+        <v>0.001841892578654251</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.004543873438331247</v>
+        <v>0.001994229089990556</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.003111122771287122</v>
+        <v>0.002093442333558596</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001848062952746453</v>
+        <v>0.001611538690687729</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002002758261814422</v>
+        <v>0.001609510518642115</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0008970667709724759</v>
+        <v>0.0008143458794247769</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001908376168331545</v>
+        <v>0.003213412900010043</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001617068762559795</v>
+        <v>0.0001022211069233947</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002232548490898771</v>
+        <v>0.003065183258956416</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.009286183194687292</v>
+        <v>0.0009097487812578684</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.00137198811086946</v>
+        <v>0.001118795334302373</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001135002647084486</v>
+        <v>0.0008847040327174289</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001686323568270702</v>
+        <v>0.0008379945165158841</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.000368282487291616</v>
+        <v>0.0002437678852609366</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003402433611537387</v>
+        <v>0.002070764123271823</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.004696133339313756</v>
+        <v>0.001496417583923721</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.007998842643711394</v>
+        <v>0.001076135799203904</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.008062953516370241</v>
+        <v>0.001970317854297873</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002496635918148205</v>
+        <v>0.000384181045328165</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0004953969305474404</v>
+        <v>0.0005287732155487154</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.004339406525296304</v>
+        <v>0.002447164320206046</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002208578026253647</v>
+        <v>0.001468100370112527</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0002382206598157012</v>
+        <v>0.000222000752963658</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0004523629795418454</v>
+        <v>0.0001477202823943476</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001894794224918218</v>
+        <v>0.001921235630856322</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.005525270891066854</v>
+        <v>0.001594260353924873</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0002799127838585228</v>
+        <v>0.000523683862356316</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001752788638231006</v>
+        <v>0.001182985744286669</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.007867050620254338</v>
+        <v>0.001519561200241738</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001653131928368899</v>
+        <v>0.0009162716741749383</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.004886194002099156</v>
+        <v>0.002105923037168435</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002017014737400502</v>
+        <v>0.0009581357486129312</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.00165186765351867</v>
+        <v>0.001408544322183245</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.00163881883241701</v>
+        <v>0.001206410848491835</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002713594503029266</v>
+        <v>0.0001318769154582692</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001004263207224255</v>
+        <v>0.0006709079345057913</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003184945197440984</v>
+        <v>0.002084488762492261</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004009555551245908</v>
+        <v>0.001470937385720136</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.005399028921560632</v>
+        <v>0.001814519510738865</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0007416420073057813</v>
+        <v>0.0002382897045853931</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0004613237026098953</v>
+        <v>0.0003764850000298638</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001734114978798144</v>
+        <v>0.0006738197749704959</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003522486177982105</v>
+        <v>0.002133526102600406</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.004103493545743612</v>
+        <v>0.001604381912213261</v>
       </c>
       <c r="DV4" t="n">
-        <v>5.983274082072875e-05</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0004063529133849725</v>
+        <v>0.0002407085451759224</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0015497092375366</v>
+        <v>0.0007731210742389224</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.006027005257318498</v>
+        <v>0.00276589380080472</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0004235811532478439</v>
+        <v>0.00042363716298863</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001697919390133647</v>
+        <v>0.001798717965341064</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.005360934176171426</v>
+        <v>0.001966841354744693</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001377527416771847</v>
+        <v>0.0007875961559787281</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001273834973041371</v>
+        <v>0.0008747937149447268</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0002158722057454358</v>
+        <v>0.0001642718491342529</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001434208184723001</v>
+        <v>0.0006249018884349433</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001831125471325556</v>
+        <v>0.0006914427619374948</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.000698988431968047</v>
+        <v>0.0004596029243454541</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002284480092074789</v>
+        <v>0.001360093685023349</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001006011289343544</v>
+        <v>0.0007885242455202301</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001146477157211585</v>
+        <v>0.001539712576555341</v>
       </c>
       <c r="EL4" t="n">
-        <v>4.285316401476686e-05</v>
+        <v>8.317180160344516e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0003467064969493796</v>
+        <v>0.0003313965996902161</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004145943173802102</v>
+        <v>0.0002856178808084441</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001063300106324389</v>
+        <v>0.0003976569657821165</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001694557974778385</v>
+        <v>0.0005332428364677071</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0001873923533213956</v>
+        <v>0.0002273258876003581</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001308234762007924</v>
+        <v>0.0003970522392347456</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001539838809586013</v>
+        <v>0.001112854412481137</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001351080357245633</v>
+        <v>0.0008264146679318417</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0002399758510481149</v>
+        <v>0.000348620535031352</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0007092283172739745</v>
+        <v>0.0006265817719455564</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001799182567444799</v>
+        <v>0.0005745728928315509</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0009184737947045245</v>
+        <v>0.0006124713993328689</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004627249357326502</v>
+        <v>-0.01086304565144954</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.002223742730071831</v>
+        <v>-0.002139384116693699</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002465844718427213</v>
+        <v>-0.002722613709160759</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.003010605542251099</v>
+        <v>-0.005831389536821075</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001099633455514848</v>
+        <v>-0.001393841166936816</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.003414028553693327</v>
+        <v>-0.002852512155591613</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.004231922692435841</v>
+        <v>-0.01115396978463513</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01272909030323226</v>
+        <v>-0.01092896174863384</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.003198933688770422</v>
+        <v>-0.004379062606910733</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.000773445053174393</v>
+        <v>-0.0006085842408712683</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0004034761018001043</v>
+        <v>-0.0003843689942344963</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003448275862069006</v>
+        <v>-0.005644885391720866</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01726091302899034</v>
+        <v>-0.009450337512053975</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00866377874041988</v>
+        <v>-0.02159280239920031</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.003831679781046871</v>
+        <v>-0.002126973896229412</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.008572349339349083</v>
+        <v>-0.004710375556970047</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004036948340745794</v>
+        <v>-0.003898700433188984</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.008708226221079718</v>
+        <v>-0.02402532489170279</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0009609224855862131</v>
+        <v>-0.002545923300032193</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00371556694426648</v>
+        <v>-0.003694834074580933</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.004131966688020561</v>
+        <v>-0.01956014661779408</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006021780909673246</v>
+        <v>-0.002634279849469756</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005834885164494074</v>
+        <v>-0.003375120540019239</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001831619537275098</v>
+        <v>-0.003921568627450922</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003619474695707847</v>
+        <v>-0.001321301965839461</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.006509829197550799</v>
+        <v>-0.00493071221398641</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.002610377054463464</v>
+        <v>-0.0003222687721559536</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.006964345218260592</v>
+        <v>-0.003696560591449638</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.001281229980781529</v>
+        <v>-0.0251366120218579</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.004252017380508987</v>
+        <v>-0.02484731597557053</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.008475668707702267</v>
+        <v>-0.002796528447444524</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0009000321440051029</v>
+        <v>-0.001864352298296312</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001740251369642332</v>
+        <v>-0.0007367072389493301</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.003939782190903229</v>
+        <v>-0.001285760205721598</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01325263811297327</v>
+        <v>-0.02295081967213111</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01012536162005782</v>
+        <v>-0.02375441980070714</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002665778073975378</v>
+        <v>-0.002565811396201312</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.008860759493670888</v>
+        <v>-0.006397536777283641</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.001953875720691833</v>
+        <v>-0.009225329476052691</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.004705124073477329</v>
+        <v>-0.009675345548055259</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002282224365155871</v>
+        <v>-0.001761691223574591</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003587443946188307</v>
+        <v>-0.002139384116693699</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.008552210121716896</v>
+        <v>-0.004836643177450317</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.004932735426008949</v>
+        <v>-0.0006997667444185396</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.006831056314561823</v>
+        <v>-0.006010928961748607</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.004113110539845788</v>
+        <v>-0.003921568627450934</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.005508039685254884</v>
+        <v>-0.003250085528566571</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004801804705124135</v>
+        <v>-0.003041589075108641</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0009643201542911761</v>
+        <v>-0.001385755720270654</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.00265855221012169</v>
+        <v>-0.002217936354869787</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.001241464928615743</v>
+        <v>-0.003306320907617533</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.007897367544151957</v>
+        <v>-0.02369210263245587</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.004804612427930788</v>
+        <v>-0.009996785599485669</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0003843689942344852</v>
+        <v>-0.0009400324149108852</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0008894970920287348</v>
+        <v>-0.000551053484602948</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.006164611796067976</v>
+        <v>-0.001899366877707465</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.00612310667096363</v>
+        <v>-0.00473175608130626</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.018593802065978</v>
+        <v>-0.006897700766411208</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001889814221652775</v>
+        <v>-0.001950051317139945</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.007412181759587544</v>
+        <v>-0.008926844988720529</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.003971812940422781</v>
+        <v>-0.002832389203598829</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.007430856381206274</v>
+        <v>-0.01166277907364214</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002274183215887315</v>
+        <v>-0.00129659643435982</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003222687721559836</v>
+        <v>-0.001478624236579829</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.004565144951682754</v>
+        <v>-0.007597467510829748</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.001611343860779935</v>
+        <v>-0.004660880745740892</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.006982703395259427</v>
+        <v>-0.001815235008103755</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.001221079691516724</v>
+        <v>-0.002199266911029696</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.006021780909673258</v>
+        <v>-0.00369529983792547</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002786675208199907</v>
+        <v>-0.001134521880064854</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002827763496143998</v>
+        <v>-0.001466177940686464</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.003729045501197415</v>
+        <v>-0.0005664778407197702</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0003241491085899218</v>
+        <v>-3.332222592469236e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.007815502882767444</v>
+        <v>-0.002360588436537814</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.008024492426683894</v>
+        <v>-0.003455354088265494</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.005961972284885641</v>
+        <v>-0.005186385737439225</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.002292165583304817</v>
+        <v>-0.003147451248717092</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001998066387367115</v>
+        <v>-0.002178090967328672</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001665598975015992</v>
+        <v>-0.002171799027552701</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.01247180148243641</v>
+        <v>-0.003215874101950056</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.007615681233933169</v>
+        <v>-0.006123845364351721</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003278688524590112</v>
+        <v>-0.003760129659643463</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.005605381165919254</v>
+        <v>-0.002820097244732611</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002429011289770788</v>
+        <v>-0.0007131280388979255</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.003351955307262544</v>
+        <v>-0.003792544570502465</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0003203074951954044</v>
+        <v>-0.0003079028395484351</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.004618542593226138</v>
+        <v>-0.008073896681491643</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.02824550128534705</v>
+        <v>-0.001537475976937896</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001413881748072021</v>
+        <v>-0.002360588436537825</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.003351595230422222</v>
+        <v>-0.001620745542949775</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.004189494038027775</v>
+        <v>-0.0005896958410924969</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0009345794392523809</v>
+        <v>-9.60922485586324e-05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.008217853689977472</v>
+        <v>-0.003250085528566582</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01423979427836705</v>
+        <v>-0.002086897023605905</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.02104755784061699</v>
+        <v>-0.002106969205834685</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.02005141388174809</v>
+        <v>-0.005303760848601713</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0004965859714462728</v>
+        <v>-0.0003182686187141459</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0003203074951953711</v>
+        <v>-0.00110210696920584</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.01082639333760407</v>
+        <v>-0.003865891207663385</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.006085842408712317</v>
+        <v>-0.0007089912987431002</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0004774029280712355</v>
+        <v>-0.0002999000333222312</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0002546148949713389</v>
+        <v>-0.0002578150177247384</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.002449242668385487</v>
+        <v>-0.0007089912987431113</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01706298200514141</v>
+        <v>-0.001832208293153292</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0004789599726308546</v>
+        <v>-0.0009237085186452609</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.00128907508862397</v>
+        <v>-0.0007779578606159187</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.02278277634961442</v>
+        <v>-0.002025072324011523</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.004210864673738301</v>
+        <v>-0.001353528843055074</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01425368353619473</v>
+        <v>-0.003147451248717104</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.004370179948586139</v>
+        <v>-0.001505302771125594</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.003694834074580911</v>
+        <v>-0.00392220421393843</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.004178720668595248</v>
+        <v>-0.002052685596989434</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0002332555814728465</v>
+        <v>-0.000171057133082464</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.001933612632935933</v>
+        <v>-0.001847649918962757</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.008392056374119151</v>
+        <v>-0.004998333888703787</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.008419023136246795</v>
+        <v>-0.004131966688020472</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01751285347043705</v>
+        <v>-0.00443185604798404</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0005276225946616586</v>
+        <v>-0.0005131713992473808</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0005834683954619279</v>
+        <v>-0.0002546148949712723</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0002999000333222312</v>
+        <v>-0.001539514197742065</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.01070051413881751</v>
+        <v>-0.00538116591928246</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.009672236503856036</v>
+        <v>-0.003235105701473384</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0.0001710571330824528</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0008676092544987246</v>
+        <v>-0.0004511762810183173</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.003694834074580933</v>
+        <v>-0.000576553491351739</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01844473007712083</v>
+        <v>-0.006842285323298014</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0006445375443120072</v>
+        <v>-0.0009921313718782132</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.003865891207663363</v>
+        <v>-0.005121555915721276</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.01751285347043706</v>
+        <v>-0.00515695067264571</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.002818705957719392</v>
+        <v>-0.002204213938411714</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.002824332712600852</v>
+        <v>-0.002495948136142678</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0001601537475977022</v>
+        <v>-0.000171057133082464</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.001089045483664286</v>
+        <v>-0.00163356822549644</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.005576462538487837</v>
+        <v>-0.002155319876838879</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0001921844971172426</v>
+        <v>-0.0008593252705282328</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.00377962844330556</v>
+        <v>-0.002700096432015386</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001520794537554304</v>
+        <v>-0.001708024492426652</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.003569211669770323</v>
+        <v>-0.002495948136142634</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0001281229980781617</v>
+        <v>-0.0002593192868720173</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0004789599726308214</v>
+        <v>-0.0006207324643079159</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0006750241080038077</v>
+        <v>-0.0001241464928615876</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.001573725624358524</v>
+        <v>-0.0006482982171799101</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.003084832904884349</v>
+        <v>-0.001361426256077825</v>
       </c>
       <c r="ER5" t="n">
-        <v>-6.842285323298558e-05</v>
+        <v>-0.0003523382447148782</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0002578150177248162</v>
+        <v>-9.60922485586324e-05</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.00188006482982167</v>
+        <v>-0.002702702702702719</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.002402306213965477</v>
+        <v>-0.001332889036987694</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0004189494038028263</v>
+        <v>-0.000366544485171616</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001707014276846652</v>
+        <v>-0.001542912246865913</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.001441383728379297</v>
+        <v>-0.001166277907364233</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001793721973094153</v>
+        <v>-0.0004178720668594926</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.003846323135591043</v>
+        <v>-0.003454636152998811</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0007967929288500792</v>
+        <v>-0.0007370186919139683</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.001841768097373511</v>
+        <v>-0.0005334404219372396</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001807462969589402</v>
+        <v>-0.002144847867839328</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0004715330685983787</v>
+        <v>-0.0001281720300022105</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001171013415399402</v>
+        <v>-0.001765471751671804</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001457450075051084</v>
+        <v>-0.002295626783623367</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.003955797565663066</v>
+        <v>-0.002292082549439189</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002352707972845797</v>
+        <v>-0.001447300115595107</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.000231597835574518</v>
+        <v>-0.0001290928759405341</v>
       </c>
       <c r="L6" t="n">
-        <v>1.606683804626363e-05</v>
+        <v>4.737772448095146e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001730292987877022</v>
+        <v>-0.002074813283315288</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.008347321449967322</v>
+        <v>-0.002336344271737542</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004228058936579109</v>
+        <v>-0.002091933938599197</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.002105220708310426</v>
+        <v>-0.0004564381806533762</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.00255103715607719</v>
+        <v>-0.001536118994532695</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.002344781281132541</v>
+        <v>-0.001386627251546996</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.005097729541786278</v>
+        <v>-0.004950255298671286</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0003802036107566242</v>
+        <v>-0.0009509110160818402</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001177164196973288</v>
+        <v>-0.001357206486211307</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001486128980999504</v>
+        <v>-0.003074818149330771</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001378782930980776</v>
+        <v>-0.001166360548914647</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001399306414998647</v>
+        <v>-0.0007960466380438181</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0004656943923865619</v>
+        <v>-0.0007850475684850145</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0006417991725392647</v>
+        <v>-0.0002309802761364304</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001519745734303435</v>
+        <v>-0.001171963661787745</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0008175937926432564</v>
+        <v>0.0001062806130354116</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002974425666465741</v>
+        <v>-0.002483928056439039</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0005183300470429003</v>
+        <v>-0.001416117549580564</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0004332976931460481</v>
+        <v>0.001441286513647189</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00255312085575464</v>
+        <v>-0.00156453637206177</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0004442389908133476</v>
+        <v>-0.0006064558017390642</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0006654024628238803</v>
+        <v>-0.0002628094678928827</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.002184350838902915</v>
+        <v>-0.0002490102580739728</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002082525978063957</v>
+        <v>-0.005316598261721856</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.003231396848725099</v>
+        <v>0.002173417305108238</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0008332808239078643</v>
+        <v>-8.005992701205223e-05</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.003995836002562449</v>
+        <v>-0.001182866779952743</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001361200012360833</v>
+        <v>-0.0009392332719264235</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002151762802382592</v>
+        <v>-0.001916151354526607</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001929012131553043</v>
+        <v>-0.0009888602032256304</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0003979537301806058</v>
+        <v>0.0006314447503097398</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.001516163947913182</v>
+        <v>0.002045903075947839</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0006261435142261296</v>
+        <v>-0.0001933612632935566</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.00226433455487777</v>
+        <v>-0.002327319477914388</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0007410684823049186</v>
+        <v>-0.0008650811744672026</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001371301930420363</v>
+        <v>-0.0007955873676538383</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.002184386847776968</v>
+        <v>-0.001851335791273759</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0004858916665912011</v>
+        <v>-0.0005040141802515275</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001851838693276664</v>
+        <v>-0.0006406494885748543</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0005273814144507449</v>
+        <v>-0.001172204119613199</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.001617552850736698</v>
+        <v>-0.001132001295983215</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.001601935725191683</v>
+        <v>-0.0006238641367708019</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.187783378345021e-05</v>
+        <v>-0.0002891717092427609</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0001991217743444851</v>
+        <v>-0.0003347783604575744</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.000322174755334309</v>
+        <v>-0.00172706090654158</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.003185687520667299</v>
+        <v>-0.002962497721555513</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002244413049768398</v>
+        <v>-0.0007450237060483228</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0001909611712284765</v>
+        <v>-0.001026821223822783</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.004288619261434379</v>
+        <v>0.0009304916298160937</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0005230003078173035</v>
+        <v>-0.0002006892476492328</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.003566739155521781</v>
+        <v>-0.001850569031677437</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0002790986698171626</v>
+        <v>-0.0004879592110526771</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.00138940711916612</v>
+        <v>-0.0001569890967371451</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001775692418334238</v>
+        <v>-0.003364484750000704</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.00115769028453066</v>
+        <v>-0.001707773660445014</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001461881965611495</v>
+        <v>-0.0002194785749023487</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0003055894552625338</v>
+        <v>-0.000304292120435587</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001212920885375449</v>
+        <v>-0.0009093124185065137</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.001465532196883812</v>
+        <v>-0.0006337714021322522</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0006345619781735868</v>
+        <v>-0.0004323847709100825</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.00239492628279434</v>
+        <v>-0.0003176343321709047</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0001106702811352389</v>
+        <v>-2.327746741154768e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001271288717740146</v>
+        <v>-0.001387768617996141</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.00163467881782639</v>
+        <v>-0.0007338654571901444</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0008687046662429893</v>
+        <v>-0.002167979586688134</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0002736981287187412</v>
+        <v>-0.0008743849652491587</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.000487806295316548</v>
+        <v>-0.0001031150306794931</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001119091773696118</v>
+        <v>-0.0004983256924785517</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.00283278775681767</v>
+        <v>-0.002115720892539263</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001581536466308059</v>
+        <v>-0.0006619414549375285</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001617670188698126</v>
+        <v>-0.001133205725349151</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001147142224878575</v>
+        <v>-0.001339029305257997</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0009598963344870593</v>
+        <v>-0.0003862812392710052</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002355895047906789</v>
+        <v>-0.001180869765776457</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-4.774029280713021e-05</v>
+        <v>-2.410800385728162e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0008136492127548855</v>
+        <v>0.0001118542378816839</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.00227989716722575</v>
+        <v>-0.000192848537282464</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0004651181503773389</v>
+        <v>-0.0003446136963937502</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0001995140278826107</v>
+        <v>-0.0005597516351840498</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0006900302968816246</v>
+        <v>-0.000334111459938724</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.0002569255298973227</v>
+        <v>8.552856654123198e-06</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.001612835226182341</v>
+        <v>-0.001305188527231674</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.004069278082853822</v>
+        <v>-0.00124435653600207</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.00239916943598045</v>
+        <v>-0.001517615058961894</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.005112091623427392</v>
+        <v>-0.0008995010760329048</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0001585028733152333</v>
+        <v>-6.435569058313994e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0001034882729941483</v>
+        <v>-0.0001577091724649649</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.006435053253823752</v>
+        <v>-0.001469440484583229</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.00164994610294586</v>
+        <v>-0.0005596307714262698</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0002899079255483383</v>
+        <v>0</v>
       </c>
       <c r="DA6" t="n">
-        <v>-6.406149903909753e-05</v>
+        <v>-9.488790662220969e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0007441032633848821</v>
+        <v>-0.0002984517250155472</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.001421267985250391</v>
+        <v>-0.001133341189842799</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.000240230621396531</v>
+        <v>-2.387014640355678e-05</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0001479953609504508</v>
+        <v>0.0001281462976028352</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.003278719243412412</v>
+        <v>-0.001443397457071335</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.001217508185209809</v>
+        <v>-0.0007516004254876557</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.004051417500835872</v>
+        <v>-0.002201502641791234</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.00277094812228062</v>
+        <v>-0.001188654885026733</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.001769698910954556</v>
+        <v>-2.954880571513496e-05</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.001360157028984865</v>
+        <v>0.0001761691223574502</v>
       </c>
       <c r="DL6" t="n">
-        <v>-7.96671585145986e-05</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0007428360276144186</v>
+        <v>-0.0006935810853148539</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.003177680898492727</v>
+        <v>-0.003282731324827079</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.004483894001121713</v>
+        <v>-0.002058085010523858</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.002697472948633969</v>
+        <v>-0.001781487169180859</v>
       </c>
       <c r="DQ6" t="n">
-        <v>8.007687379882333e-06</v>
+        <v>-0.0002405248129405623</v>
       </c>
       <c r="DR6" t="n">
+        <v>-0.000136516660106778</v>
+      </c>
+      <c r="DS6" t="n">
         <v>0</v>
       </c>
-      <c r="DS6" t="n">
-        <v>-2.327746741154768e-05</v>
-      </c>
       <c r="DT6" t="n">
-        <v>-0.002229980671968512</v>
+        <v>-0.001683272666082156</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.005242764281554305</v>
+        <v>-0.0008528444111926158</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0005940307188076754</v>
+        <v>-0.000256185364548478</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0005799102626692449</v>
+        <v>-0.0001780516768436213</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.003235954960141871</v>
+        <v>-0.002497355995989489</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.551831160769846e-05</v>
+        <v>-0.0003823810896652374</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.001436179733460372</v>
+        <v>-0.0004489060705518549</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.00254620350692325</v>
+        <v>-0.002691290930276871</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0001942539537937743</v>
+        <v>-0.0009068096853833474</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0009535838209308561</v>
+        <v>-0.0006006952693937556</v>
       </c>
       <c r="EE6" t="n">
-        <v>-3.361528543022463e-05</v>
+        <v>8.033419023137368e-06</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.000359887184886562</v>
+        <v>-0.001310365738345704</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0004570265637416332</v>
+        <v>-0.0006350975518238961</v>
       </c>
       <c r="EH6" t="n">
-        <v>3.103662321539691e-05</v>
+        <v>-8.784232317954332e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001431897855550518</v>
+        <v>-0.001917550373617394</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0009928926640675297</v>
+        <v>-0.000711912499445233</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0008079901762140518</v>
+        <v>0.0001544061439268579</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-3.178221794349623e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0001862197392923648</v>
+        <v>-0.0003226182722120552</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0002154619645287764</v>
+        <v>-2.431118314425163e-05</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.000175635789280365</v>
+        <v>-0.0001680764271511093</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.001064897200440246</v>
+        <v>-0.0008437623006277179</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-6.733251468450941e-05</v>
+        <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0004742153420935258</v>
+        <v>-6.27700226339456e-05</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.001323012775821009</v>
+        <v>-0.0001433737941574253</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001906933076610356</v>
+        <v>-5.605381165920409e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.00094200705097566</v>
+        <v>-0.0006872851455803825</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.001241255584034431</v>
+        <v>-0.0009566095934856355</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0004991542470783538</v>
+        <v>-1.609256968952421e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.001776222057107613</v>
+        <v>-0.0008618989248494636</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003326745848923507</v>
+        <v>-0.0001591343093570674</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0005460715316648768</v>
+        <v>0.0002869514759630654</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0005285073670724006</v>
+        <v>-5.154043857678035e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0002907940295139966</v>
+        <v>1.601537475978132e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0007708953931256312</v>
+        <v>-0.0003269978544043485</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002727143934101062</v>
+        <v>-0.0009750256585699725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00143336451360167</v>
+        <v>-0.001379352600040723</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.00153520631824568</v>
+        <v>6.474794597529642e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.845389957555123e-05</v>
+        <v>4.814905085233079e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001320765769758314</v>
+        <v>0.0002454306022753816</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0009780413405435285</v>
+        <v>-0.001691615038916011</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.003019158098967883</v>
+        <v>0.00025989552888111</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0008614095249835585</v>
+        <v>-0.0006418501092668061</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0009642736735639868</v>
+        <v>0.0004734862028693664</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0004880389322125144</v>
+        <v>0.002136112647481763</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.001022027613727511</v>
+        <v>0.000610689616990584</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.001603307221460165</v>
+        <v>-0.002891544820009972</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001449850253840979</v>
+        <v>-0.0002377453056361556</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0002893554480042304</v>
+        <v>-0.0004648381234253762</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0005964011532924528</v>
+        <v>-0.001371295049406296</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0007067740959316004</v>
+        <v>0.0001767352185089777</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.000866013892617129</v>
+        <v>-0.0005444567822395884</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.774367604457602e-05</v>
+        <v>-0.0003996337339131073</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003326419066931441</v>
+        <v>0.0002280804739881237</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.435004160503682e-05</v>
+        <v>0.001461982025401082</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0004946416287197664</v>
+        <v>0.0001776047454345842</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0004325773703648395</v>
+        <v>-0.001346504313911706</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001819895799185251</v>
+        <v>0.0005599622319552522</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001853586293857457</v>
+        <v>0.003975391168647324</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0002742332996637787</v>
+        <v>0.0008194602036463994</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0002864417568427702</v>
+        <v>-0.000211150578116337</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.53696365572109e-05</v>
+        <v>3.213367609257723e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.415255742812099e-05</v>
+        <v>0.000490714952278637</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.0003500332766781634</v>
+        <v>-0.0003307883573533565</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.007002613024098298</v>
+        <v>0.01012106480079988</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0001914708903487883</v>
+        <v>0.0001761691223574669</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0003739112980815361</v>
+        <v>-0.000766698974358615</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.041619838222713e-06</v>
+        <v>0.0001166233673717987</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.001477545067723534</v>
+        <v>-6.23284540300584e-05</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0007408385578562438</v>
+        <v>-0.0006094336580475035</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0006589056247051139</v>
+        <v>0.001615871796738222</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.003926665259913231</v>
+        <v>0.003627536126351871</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0003365342456001785</v>
+        <v>0.0002130708763766698</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0001626228853449041</v>
+        <v>-0.0004786301849557528</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.000428393467787247</v>
+        <v>-0.0003352014878904463</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0007199447858341312</v>
+        <v>0.0004989736662593224</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.001697629724535571</v>
+        <v>-0.0007563188592936033</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0003857418881068941</v>
+        <v>0.0002085601148825167</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0004394494629627099</v>
+        <v>0.0002838031773072125</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0008944061140414017</v>
+        <v>-0.0003521117334678914</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.0006976021902369345</v>
+        <v>-0.0008648302370275474</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003196014689498994</v>
+        <v>0.001476344218800613</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0002050292095314987</v>
+        <v>-0.0001650957212197546</v>
       </c>
       <c r="BD7" t="n">
-        <v>-7.896984568208642e-05</v>
+        <v>-9.537864179019471e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0004146666987449976</v>
+        <v>-0.0002515841443545885</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.000354911409040043</v>
+        <v>0.0003373003084667981</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.001263361281755832</v>
+        <v>-4.674025444661997e-05</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0004282598678300664</v>
+        <v>8.029803855466036e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0009917181162295728</v>
+        <v>0.001968169432489081</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002460988799688424</v>
+        <v>0.0001769216207551438</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.001051902744869781</v>
+        <v>-0.001000526346391634</v>
       </c>
       <c r="BL7" t="n">
-        <v>8.058361961463256e-05</v>
+        <v>-0.0001241464928615821</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0004496141488631199</v>
+        <v>-0.0001133903863555441</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001352155949182637</v>
+        <v>0.0008488148622677771</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0004042663404561331</v>
+        <v>-0.0005272909204262488</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0002730296935950172</v>
+        <v>0.0003505032558818733</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0004969164971045936</v>
+        <v>0.0005930783787881699</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0003552984629999367</v>
+        <v>0.0004931124713589086</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0007144374609541815</v>
+        <v>-0.0001144370933182204</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.000114592939078767</v>
+        <v>0.0004463916167923299</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0002896213103639134</v>
+        <v>0.0005942975921390369</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.0004187836596576677</v>
+        <v>-0.0005805560008718346</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0002153029921053373</v>
+        <v>-0.0003854476965627518</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0001769037220808678</v>
+        <v>-0.0003363228699551635</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.000211360694324042</v>
+        <v>-0.0001448588588489341</v>
       </c>
       <c r="CB7" t="n">
-        <v>-1.23169630275588e-06</v>
+        <v>0.001922874950288827</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0006375143796825633</v>
+        <v>0.000367323041852119</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.0001875745610437352</v>
+        <v>3.213269334363389e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0002722613709160881</v>
+        <v>-0.0005686004809185685</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0008005216365368107</v>
+        <v>-0.0003856609228882368</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0005073915947506558</v>
+        <v>-0.0005774595363397195</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.000197194983775445</v>
+        <v>6.010742777258217e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.001568107029891036</v>
+        <v>-0.0003390223473689003</v>
       </c>
       <c r="CJ7" t="n">
-        <v>3.158514965396763e-05</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0002561440523322189</v>
+        <v>0.0003211900698276371</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0009794028266225496</v>
+        <v>0.0003953806189365139</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0001275113351337898</v>
+        <v>-0.000204899005524134</v>
       </c>
       <c r="CN7" t="n">
-        <v>-3.227945800100551e-05</v>
+        <v>-0.0002660590430925702</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0004034254985837427</v>
+        <v>-3.269614562543821e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0001300602126858896</v>
+        <v>0.0001444325643820299</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0004520984680886131</v>
+        <v>0.0005213605189410054</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0006271315879083749</v>
+        <v>-0.0008200449976024538</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0006534507067245287</v>
+        <v>-0.0005810390863350279</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.001754116042355902</v>
+        <v>-0.0002642064166588464</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>3.20873773312913e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>4.952968135418789e-05</v>
+        <v>3.203074951952933e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0008846064882238491</v>
+        <v>-0.0009854041797550004</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.0006970002343518356</v>
+        <v>-0.0002419868923766666</v>
       </c>
       <c r="CZ7" t="n">
+        <v>1.551831160769846e-05</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>-1.620745542950663e-05</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.0003516295516912571</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0.0003998667110963194</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.0001935412951481252</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.0004010019284322542</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.0004287331712546305</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0.0005525851061587872</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-0.0007898061771654252</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-7.021010134581344e-05</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.0002235016398683842</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.0007111536856422406</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1.611343860780656e-05</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0.0006165215657021107</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-0.001196291829355461</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.0009400561827977883</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0.0008820305132292538</v>
+      </c>
+      <c r="DQ7" t="n">
         <v>-1.601537475977022e-05</v>
       </c>
-      <c r="DA7" t="n">
-        <v>1.607200257150998e-05</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0.0001184424208678259</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-6.049276911871958e-05</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>-3.199305870932866e-05</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0.0001603265917296481</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>-0.0008403243252110004</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>-0.0003544956493716278</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>-0.00102589002961328</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>-0.001281229980781568</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>-0.0008636206696240767</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>-0.0003521689749185541</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>9.587832446530386e-05</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>0.0001280097424546323</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>-0.0009766320288737639</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-0.001227091861403246</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>-0.001468623118167916</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>6.440140576947639e-05</v>
-      </c>
       <c r="DR7" t="n">
-        <v>7.818668503858373e-05</v>
+        <v>-1.611343860778991e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>9.654082996219394e-05</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.001350471304379297</v>
+        <v>-0.0009271209862563023</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0004097035474306899</v>
+        <v>-0.0004338511079765683</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-5.02268013762519e-05</v>
+        <v>-8.552856654124308e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0001603596007436925</v>
+        <v>0.0006780040708793678</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.001813558203645249</v>
+        <v>-0.0004502908703493347</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0001283288512241576</v>
+        <v>3.391133631551746e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.001024983984625255</v>
+        <v>-0.0001761691223574779</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.001298774306458617</v>
+        <v>-0.00117751955102432</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0002152205787719907</v>
+        <v>-0.0002296899319763846</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0.0006145670708171513</v>
+        <v>-3.213367609253836e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>6.53529754442328e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0001990353081271157</v>
+        <v>-0.0005674376311227026</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0001779702490683654</v>
+        <v>-0.0003860977202620408</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0002192620705859016</v>
+        <v>-3.203074951952933e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0004198895720197881</v>
+        <v>-0.0009885611479922951</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0003220909371334235</v>
+        <v>-0.0001436286537176201</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.0004439525020563217</v>
+        <v>0.0004099379227770261</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0.0001157708943559155</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001123144592133252</v>
+        <v>1.611343860780656e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-9.832365471045822e-05</v>
+        <v>-5.062907708959785e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0005445227418321764</v>
+        <v>-0.0004829816233574036</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-1.601537475977022e-05</v>
+        <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0001734698825037739</v>
+        <v>0.0002510356179160289</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0004991903929111141</v>
+        <v>0.0002084057250230031</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.0002882767456758694</v>
+        <v>-0.0002717283719395558</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0002741051730246524</v>
+        <v>-0.0005951185261602264</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0001607148611899423</v>
+        <v>0.0002434593124094442</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0003243841506441886</v>
+        <v>0.001495811536044705</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008535092970153174</v>
+        <v>0.0003048438605344012</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005012550203392779</v>
+        <v>0.0009664568122565415</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004939953943059794</v>
+        <v>0.002101014705073093</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001774117802375963</v>
+        <v>0.0002103277431496297</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001478765350090477</v>
+        <v>0.001290143713149433</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009440688534321368</v>
+        <v>0.0006290902410808318</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002124062727564269</v>
+        <v>-0.0002562459961562763</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003690868224847543</v>
+        <v>0.001253796934869203</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003452649162289406</v>
+        <v>0.0002195419652170405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002092295422812973</v>
+        <v>0.0008002521967279797</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0004031566384469886</v>
+        <v>-0.0004922145032326602</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002916554892814094</v>
+        <v>0.003032108223826438</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004578703192863187</v>
+        <v>-0.000104737350950701</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0003386764023078525</v>
+        <v>0.0006186171632461213</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001966036503633437</v>
+        <v>0.003611470753111579</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.0006666809820854242</v>
+        <v>0.001442357291899049</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001520399418226312</v>
+        <v>0.001507944016429966</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.056719303900506e-06</v>
+        <v>8.326672684688675e-18</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0004043038678260447</v>
+        <v>8.781908281593198e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002189416735307537</v>
+        <v>0.003692001703988099</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006317101518314106</v>
+        <v>0.0006735969632815891</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.000149950016661099</v>
+        <v>0.0001464998770899756</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0004497046190379605</v>
+        <v>-2.459930414888123e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004175067891378579</v>
+        <v>0.001876122970754326</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001328875497576651</v>
+        <v>0.003574543101074906</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.661381400341332e-05</v>
+        <v>0.000473558463749954</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001497020006990699</v>
+        <v>0.002592860156792484</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.006240423464835432</v>
+        <v>0.003414106715866982</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.006750455919029058</v>
+        <v>0.00436566413272595</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002283638320432565</v>
+        <v>0.002457163117426511</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0008418368452922153</v>
+        <v>0.0003523382447148892</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0003364927533904327</v>
+        <v>0.0004186598274629722</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0003037924343341381</v>
+        <v>0.00125919096946876</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002926751991019752</v>
+        <v>0.004155519639754921</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01096407497935203</v>
+        <v>0.02015420035568908</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001181316220371406</v>
+        <v>0.000614067144729491</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00100032989325827</v>
+        <v>0.001655751030949076</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001932842611608187</v>
+        <v>0.0003843689942344464</v>
       </c>
       <c r="AO8" t="n">
-        <v>-9.636265909560571e-05</v>
+        <v>0.0008172812514322086</v>
       </c>
       <c r="AP8" t="n">
-        <v>-5.969214387995247e-05</v>
+        <v>0.000421112606400495</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00154947820278879</v>
+        <v>0.00243613817851259</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.004491914884198709</v>
+        <v>0.00630947703220211</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.073293718406649e-05</v>
+        <v>0.0004287241732739533</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0005417012325349164</v>
+        <v>0.001555231072729896</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0002324680936367257</v>
+        <v>0.0002401534264667576</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.0001524805715801214</v>
+        <v>0.00132421489808946</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.721945197092785e-06</v>
+        <v>-0.0002245497579990069</v>
       </c>
       <c r="AX8" t="n">
-        <v>-9.7959341170617e-05</v>
+        <v>0.0003390334537974077</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0005374825823916073</v>
+        <v>0.001037998462583303</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002777890000376007</v>
+        <v>0.0002403850112560058</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002258197993442035</v>
+        <v>0.001796386221943661</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004979740474238078</v>
+        <v>0.002824581376842094</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0004258851305606798</v>
+        <v>5.622876863671799e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>-8.007687379887886e-06</v>
+        <v>0.0002562974594428364</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0009855401397491693</v>
+        <v>-4.024216048317541e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002722774835917682</v>
+        <v>0.002156225309845669</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.0003554126701561244</v>
+        <v>0.0003001006179753962</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001156040390034044</v>
+        <v>0.0006333918137951811</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005096720748814388</v>
+        <v>0.005155528798813863</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001307410349223864</v>
+        <v>0.0009918318530410947</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001590518716719647</v>
+        <v>0.0006845454317709277</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0004643140846256333</v>
+        <v>0.0004466794450190631</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0001748501806288077</v>
+        <v>7.230077120825296e-05</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.003587292417962707</v>
+        <v>0.005272761080796514</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0002642536835361975</v>
+        <v>0.0003122998078155193</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0004467683485724211</v>
+        <v>0.001643639526775292</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002086370993569409</v>
+        <v>0.002090494096658749</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0.0001662644176637279</v>
+        <v>0.001464151516760923</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0001979961409404318</v>
+        <v>0.0002402306213965172</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001691660257959848</v>
+        <v>0.001241686799226393</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0007649223282551576</v>
+        <v>0.001086186148306015</v>
       </c>
       <c r="BW8" t="n">
+        <v>2.387014640356511e-05</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.0001921844971172732</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.0007850460522851378</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.00041581794666809</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.0005703948788975038</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.002853914177920561</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.00181084380851374</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.0005141568933191176</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-3.203074951954599e-05</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.0007694734673291792</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.0002645478750803149</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.0009149148593081108</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.001138218087199516</v>
+      </c>
+      <c r="CJ8" t="n">
         <v>0</v>
       </c>
-      <c r="BX8" t="n">
-        <v>9.663113894348152e-05</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.002324059570195599</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.0009394468561283841</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.0008945319294247827</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.001108578011227904</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0.001727127718974208</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0.001447379835832377</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0.0006945160598226752</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>0.0008217853689977046</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0.0004294325245983221</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>-7.264542842814748e-05</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>0.0001844356386863311</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>3.302767072927981e-05</v>
-      </c>
       <c r="CK8" t="n">
-        <v>0.0007973409187753272</v>
+        <v>0.001890458079009599</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.000355073622522864</v>
+        <v>0.0009732202990135441</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0007351899668567502</v>
+        <v>0.000256167288710113</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0003685337409774642</v>
+        <v>0.0005819504038499651</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0007173217760186007</v>
+        <v>0.001053316990960662</v>
       </c>
       <c r="CP8" t="n">
-        <v>3.361528543022463e-05</v>
+        <v>0.0002485557218366435</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0009640490167157096</v>
+        <v>0.001380796001179166</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.000183412231056887</v>
+        <v>0.0009614987275953779</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.001210452270767703</v>
+        <v>0.0004727133770346559</v>
       </c>
       <c r="CT8" t="n">
-        <v>-3.203074951954599e-05</v>
+        <v>0.000599195649217088</v>
       </c>
       <c r="CU8" t="n">
-        <v>8.012590572283596e-05</v>
+        <v>8.589924028090945e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003280918253066256</v>
+        <v>0.0001523159119515033</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0.0001441209129458221</v>
+        <v>-0.0002794025357914009</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0.0003611950763221544</v>
+        <v>0.0005365150544522995</v>
       </c>
       <c r="CZ8" t="n">
-        <v>8.042773928659263e-05</v>
+        <v>0.0001360287416339534</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0003847813234526543</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0009006436371343212</v>
+        <v>0.0005887934934165284</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.000633451734348961</v>
+        <v>0.0007078484325496598</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0001652419437370822</v>
+        <v>0.0002802690582959621</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0004737981201013097</v>
+        <v>0.0005861750713665237</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.0005594167345272822</v>
+        <v>0.001250325710517905</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0004328150960076854</v>
+        <v>-3.99369844497982e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0004531360961106152</v>
+        <v>-4.819322005133463e-05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.000589544626647917</v>
+        <v>0.0004099926499745249</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-2.252713484807156e-05</v>
+        <v>0.0003937382403760237</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0002069765459883188</v>
+        <v>0.001293705827815586</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0003397803220102469</v>
+        <v>0.0001448333831327725</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0007556810893998511</v>
+        <v>-2.4023062139647e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0008021280185275814</v>
+        <v>-8.88278305861412e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0005547287907752857</v>
+        <v>-0.0002964694683031788</v>
       </c>
       <c r="DP8" t="n">
-        <v>-4.481949965139397e-05</v>
+        <v>0.0002009829042165845</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0005826556783140591</v>
+        <v>6.983240223464859e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.000182083692753654</v>
+        <v>0.0002245381157380044</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0001514947371608677</v>
+        <v>7.206918641894101e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>1.602888166546691e-05</v>
+        <v>-0.0006993911385397289</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001386609311712009</v>
+        <v>0.0002914460767263261</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001442233145555166</v>
+        <v>8.584777699441048e-05</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0001914022079692018</v>
+        <v>0.0008799410446358097</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0002655896865635443</v>
+        <v>-3.963066160320438e-05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002495901248614874</v>
+        <v>0.000128431777797175</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0002409326698517622</v>
+        <v>3.178221794352398e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>-5.134431148559048e-05</v>
+        <v>-0.000755569806881673</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0006396382189189336</v>
+        <v>1.610031647742149e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0.0002113606943240309</v>
+        <v>0.0001041282498443347</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001205400192864081</v>
+        <v>0.0002426707947017659</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0003392037222955724</v>
+        <v>-0.0003834295448770536</v>
       </c>
       <c r="EG8" t="n">
-        <v>-8.033419023145694e-06</v>
+        <v>-3.103662321535528e-05</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0004527523083424246</v>
+        <v>0.0001829751051277723</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0006600568182317801</v>
+        <v>-8.808456117874452e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0002165017508009154</v>
+        <v>0</v>
       </c>
       <c r="EK8" t="n">
-        <v>3.940102188723928e-05</v>
+        <v>0.0009098034740408407</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>5.622369509444836e-05</v>
+        <v>2.402306213965533e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0003326765367691331</v>
+        <v>0.000296080545407637</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>6.356443588700911e-05</v>
+        <v>8.010260544208115e-05</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0004457736258638961</v>
+        <v>-9.624663841810155e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>7.232401157184488e-05</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>3.186715966113085e-05</v>
+        <v>3.376229767711736e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>-4.068417510203481e-05</v>
+        <v>0.0004250359241483564</v>
       </c>
       <c r="EU8" t="n">
-        <v>-8.068867771849342e-05</v>
+        <v>0.0003522631583712826</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0001681614349775901</v>
+        <v>0.0001629422718808254</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0001317935396454972</v>
+        <v>5.801675791017591e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0006070744524434319</v>
+        <v>-0.0002485214478351344</v>
       </c>
       <c r="EY8" t="n">
-        <v>4.998333888703855e-05</v>
+        <v>0.0005881389796848297</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002052685596989423</v>
+        <v>0.007186593619078374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001221079691516713</v>
+        <v>0.002352562036738681</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003084832904884305</v>
+        <v>0.003632272581163653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001510282776349592</v>
+        <v>0.002234636871508344</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009318766066837792</v>
+        <v>0.001304901336728226</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00382390745501282</v>
+        <v>0.003952442159383063</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002301458670988654</v>
+        <v>0.001060411311054021</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003061553335481737</v>
+        <v>0.005800837898807654</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002690437601296636</v>
+        <v>0.003728704596592769</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009237085186452499</v>
+        <v>0.001417982597486356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001393841166936816</v>
+        <v>0.003342976534876274</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004789456766313127</v>
+        <v>-0.0002482929857231753</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005186385737439225</v>
+        <v>0.01295520464067036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001063486948114689</v>
+        <v>0.0008593252705283438</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001217168481742425</v>
+        <v>0.002625607779578576</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0167470266795243</v>
+        <v>0.00912889746062362</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0006807131280389123</v>
+        <v>0.003403565640194484</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004447309055752446</v>
+        <v>0.009442475024170205</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001377322229340172</v>
+        <v>0.0007455429497568832</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0048537447765992</v>
+        <v>0.001336728198599646</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002036919159770889</v>
+        <v>0.00731550112794076</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004466580976863732</v>
+        <v>0.001546890106348753</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01388983920629492</v>
+        <v>0.004584331166609635</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0009023525620366901</v>
+        <v>0.0005800837898808142</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008073896681491633</v>
+        <v>0.004370179948586139</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02214010282776346</v>
+        <v>0.0159061696658098</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001163188504960677</v>
+        <v>0.001024983984625283</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002835965194972567</v>
+        <v>0.004948586118251963</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.008926844988720529</v>
+        <v>0.01150499516596846</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.009442353746151233</v>
+        <v>0.005031656114628425</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004596592735454874</v>
+        <v>0.004550119739993119</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.002333873581847667</v>
+        <v>0.002824332712600874</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0006158833063209191</v>
+        <v>0.003010605542251077</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001249199231261966</v>
+        <v>0.001633568225496529</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006631122959013669</v>
+        <v>0.00690642902609806</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03014586709886549</v>
+        <v>0.02846058348851643</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00246322271638727</v>
+        <v>0.002025072324011601</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.003407264545162369</v>
+        <v>0.003791773778920338</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002603664416586327</v>
+        <v>0.002832590706556393</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.005508039685254873</v>
+        <v>0.006790518898142262</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0009990331936835072</v>
+        <v>0.001197399931577115</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00328429695518303</v>
+        <v>0.004500160720025737</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01235032500855287</v>
+        <v>0.009510776599384175</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001599466844385233</v>
+        <v>0.002114029468289536</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.003061553335481748</v>
+        <v>0.008926844988720628</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0006365372374284028</v>
+        <v>0.001642148477591498</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.00294682895579752</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.005334190231362468</v>
+        <v>0.0005092297899427333</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.203074951948493e-05</v>
+        <v>0.00208689702360586</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002957248473159768</v>
+        <v>0.002702702702702675</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.004755784061696644</v>
+        <v>0.001738050900062049</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01039726877715709</v>
+        <v>0.004034761018001221</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01120422098075731</v>
+        <v>0.01630365150544527</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.00106075216972038</v>
+        <v>0.000566477840719759</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001478624236579917</v>
+        <v>0.003696560591449738</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.005772811918063325</v>
+        <v>0.003523776941498435</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01216635630043453</v>
+        <v>0.007883302296710104</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00130353817504657</v>
+        <v>0.004438237119801347</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003318508381799523</v>
+        <v>0.001089045483664264</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01616843458694956</v>
+        <v>0.006764411862712405</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.004343598055105358</v>
+        <v>0.00291734197730954</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005381888495004783</v>
+        <v>0.003899452143087401</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.004823811152925073</v>
+        <v>0.001163188504960622</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002976394115634618</v>
+        <v>0.0009609224855862241</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.007076350093109885</v>
+        <v>0.008194087403599004</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.001881628463906959</v>
+        <v>0.002803738317757054</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001670951156812317</v>
+        <v>0.008775313404050189</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01642148477591515</v>
+        <v>0.01019500513171396</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0008210742387957714</v>
+        <v>0.006493089038894273</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.004892234006158069</v>
+        <v>0.002463222716387237</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.009739633558341398</v>
+        <v>0.00678238508518163</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002855369335816282</v>
+        <v>0.003079028395484062</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.332222592469236e-05</v>
+        <v>3.241491085899106e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001037277147487847</v>
+        <v>0.001458670988654775</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.004691516709511556</v>
+        <v>0.004646721833227308</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.004455760661998776</v>
+        <v>0.007192870782940841</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001836932001289027</v>
+        <v>0.003126007089913052</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00292416452442158</v>
+        <v>0.007682417229186789</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005234348272322964</v>
+        <v>0.004173794047211743</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002217936354869876</v>
+        <v>0.002978859705317049</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.004311183144246366</v>
+        <v>0.00170802449242673</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002370275464445892</v>
+        <v>0.001377322229340139</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001579116983564255</v>
+        <v>0.002232589136954288</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0005445227418320985</v>
+        <v>0.001409352978859768</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002942182689018136</v>
+        <v>0.00707168113146901</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0003421142661649279</v>
+        <v>6.207324643079382e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003503696560591485</v>
+        <v>0.002765744751749355</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.001537475976937797</v>
+        <v>0.001546890106348742</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.003600128576020612</v>
+        <v>0.001089045483664264</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0005586592178770889</v>
+        <v>0.001018459579885445</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001799400199933376</v>
+        <v>0.001537475976937896</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0003565640194489128</v>
+        <v>0.0007638446849140834</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.004131966688020461</v>
+        <v>0.0037608486017358</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0009310986964618407</v>
+        <v>0.002100572883513729</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.002333873581847679</v>
+        <v>0.0008274984086569237</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001523500810372791</v>
+        <v>0.001965839510151523</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0002917341977309529</v>
+        <v>0.0009237085186452054</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.00122107969151668</v>
+        <v>0.000773445053174382</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0006807131280389123</v>
+        <v>0.005349661617789281</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.001458670988654787</v>
+        <v>0.004114432658309253</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001289075088623637</v>
+        <v>0.000512491992312647</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001163188504960677</v>
+        <v>0.000224215246636783</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.003857280617164927</v>
+        <v>0.00578592092574739</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002288108282307399</v>
+        <v>0.003500954805856216</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.000310366232153958</v>
+        <v>0.001127940702545971</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.004356181934657211</v>
+        <v>0.003544956493715812</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.0001332889036987695</v>
+        <v>0.001965839510151513</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001317480719794317</v>
+        <v>0.00155591572123176</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001654996817313847</v>
+        <v>0.003465511496167895</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001607200257152075</v>
+        <v>0.001055245189323373</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.002217936354869843</v>
+        <v>0.001249199231261966</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001767352185089954</v>
+        <v>0.002327746741154546</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0005765534913517278</v>
+        <v>0.0002882767456758639</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001060411311053955</v>
+        <v>0.0006158056790968147</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002282224365155916</v>
+        <v>0.0006107360977178012</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.003165611462845685</v>
+        <v>0.0003763256927813874</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0009345794392522921</v>
+        <v>0.001345291479820587</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.002152956298200492</v>
+        <v>0.0002332555814728465</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001253616200578644</v>
+        <v>0.001037277147487836</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0003203074951954044</v>
+        <v>0.001296596434359765</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001845957988542368</v>
+        <v>0.002545923300032294</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.00183220829315337</v>
+        <v>0.001877784850413788</v>
       </c>
       <c r="DV9" t="n">
-        <v>6.406149903905866e-05</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0002255881405091475</v>
+        <v>0.0002546148949713611</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.002410800385728096</v>
+        <v>0.001769087523277457</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.001799400199933376</v>
+        <v>0.003598800399866664</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0009288917360665616</v>
+        <v>0.0003565640194489461</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002057216329154632</v>
+        <v>0.001539514197742009</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0007320178230426633</v>
+        <v>0.001857783472133212</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002282224365155938</v>
+        <v>0.0003414028553693216</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001896496303439454</v>
+        <v>0.0006726457399103602</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0005896958410925301</v>
+        <v>0.0003222687721560202</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.003921568627451033</v>
+        <v>0.0001285347043701979</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001361426256077813</v>
+        <v>9.64320154291265e-05</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.00221722365038558</v>
+        <v>0.0008894970920287126</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.004885888781742254</v>
+        <v>0.001303538175046537</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001767920282867286</v>
+        <v>0.0009321761491482228</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0005785920925747701</v>
+        <v>0.003278688524590201</v>
       </c>
       <c r="EL9" t="n">
-        <v>3.214400514304216e-05</v>
+        <v>3.421142661649279e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0008427876823338898</v>
+        <v>0.0005410566518141424</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0007089912987431224</v>
+        <v>0.0007184399589462819</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.002667952426872411</v>
+        <v>0.0007448789571694147</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.003310832529733243</v>
+        <v>0.0002250080360012952</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0005834683954619279</v>
+        <v>0.000578592092574759</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001666111296234618</v>
+        <v>0.001127940702545971</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003823907455012832</v>
+        <v>0.001321301965839572</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002250080360012896</v>
+        <v>0.001960784313725527</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0002571520411443373</v>
+        <v>0.0009023525620367789</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0002593192868719729</v>
+        <v>0.0004447485460143508</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.003341902313624656</v>
+        <v>0.0006365372374284251</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001402668491276093</v>
+        <v>0.00140266849127606</v>
       </c>
     </row>
   </sheetData>
